--- a/reports/business_report.xlsx
+++ b/reports/business_report.xlsx
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>153.75</v>
+        <v>146.89</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>114.82</v>
+        <v>110.01</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>88.04000000000001</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>69.5</v>
+        <v>67.08</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>30.15</v>
+        <v>39.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>11.95</v>
+        <v>28.15</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/reports/business_report.xlsx
+++ b/reports/business_report.xlsx
@@ -10,6 +10,9 @@
     <sheet name="Customer Segments" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Sales Forecast" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Model Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Product Recommendations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Churn Risk" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Anomaly Alerts" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -575,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>146.89</v>
+        <v>152.13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -596,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>110.01</v>
+        <v>128.01</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -617,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>94.18000000000001</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -638,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>67.08</v>
+        <v>71.62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -659,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>39.4</v>
+        <v>34.57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -680,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>28.15</v>
+        <v>22.59</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1285,4 +1288,508 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>customer_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>purchased_products</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>recommended_products</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>recommendation_method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status_notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Notebook A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>None (No unseen peer products)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CF: No peer customers with similar buying patterns found (zero similarity). | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pen Set</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>None (No unseen peer products)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CF: Similar peers exist, but no unseen products remain to recommend. | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Marker Box</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>None (No unseen peer products)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CF: No peer customers with similar buying patterns found (zero similarity). | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Stapler</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>None (No unseen peer products)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CF: No peer customers with similar buying patterns found (zero similarity). | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pen Set</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>None (No unseen peer products)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CF: Similar peers exist, but no unseen products remain to recommend. | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>customer_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>order_frequency</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total_spend</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>days_since_last_order</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>churn_probability</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>retention_risk</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>model_used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Regular Customers</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>180</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6814</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Medium Risk</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Occasional Shoppers</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>144</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Medium Risk</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VIP / Loyal Customers</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>240</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Medium Risk</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>At-Risk / Fading Customers</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5921</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Medium Risk</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>At-Risk / Fading Customers</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6002</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Medium Risk</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>customer_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>detection_method</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>alert_message</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>review_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pen Set</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Isolation Forest</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Unusual sales activity detected on Order #1002: High unit quantity (10 units of Pen Set at $12.00/unit) deviates from typical purchasing patterns (score: -0.0054). Flagged for review.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Flagged for Human Review (Unverified)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reports/business_report.xlsx
+++ b/reports/business_report.xlsx
@@ -578,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>152.13</v>
+        <v>148.96</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>128.01</v>
+        <v>116.49</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>91.84999999999999</v>
+        <v>97.34</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>71.62</v>
+        <v>61.46</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57</v>
+        <v>33.79</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>22.59</v>
+        <v>9.68</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/reports/business_report.xlsx
+++ b/reports/business_report.xlsx
@@ -578,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>148.96</v>
+        <v>141.31</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>116.49</v>
+        <v>118.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>97.34</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>61.46</v>
+        <v>64.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>33.79</v>
+        <v>37.32</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9.68</v>
+        <v>13.82</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/reports/business_report.xlsx
+++ b/reports/business_report.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customer Segments" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sales Forecast" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Model Comparison" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Product Recommendations" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Churn Risk" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Anomaly Alerts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Segments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Forecast" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Recommendations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Churn Risk" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anomaly Alerts" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>141.31</v>
+        <v>138.37</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>118.66</v>
+        <v>122.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>91.15000000000001</v>
+        <v>108.74</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>64.36</v>
+        <v>68.11</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>37.32</v>
+        <v>40.39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>13.82</v>
+        <v>14.03</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1227,6 +1227,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>selection_status</t>
         </is>
       </c>
@@ -1245,6 +1250,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>N/A (sample too small)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Selected (Lowest Error)</t>
         </is>
       </c>
@@ -1263,6 +1273,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>N/A (sample too small)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Evaluated</t>
         </is>
       </c>
@@ -1280,6 +1295,11 @@
         <v>83.49079999999999</v>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>N/A (sample too small)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Evaluated</t>
         </is>
@@ -1339,7 +1359,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>None (No unseen peer products)</t>
+          <t>Pen Set, Marker Box, Stapler</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1349,7 +1369,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CF: No peer customers with similar buying patterns found (zero similarity). | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+          <t>Recommendations generated successfully.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1386,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None (No unseen peer products)</t>
+          <t>Marker Box, Notebook A, Stapler</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1376,7 +1396,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CF: Similar peers exist, but no unseen products remain to recommend. | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+          <t>Recommendations generated successfully.</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1413,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None (No unseen peer products)</t>
+          <t>Pen Set, Notebook A, Stapler</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1403,7 +1423,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CF: No peer customers with similar buying patterns found (zero similarity). | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+          <t>Recommendations generated successfully.</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1440,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None (No unseen peer products)</t>
+          <t>Pen Set, Marker Box, Notebook A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1430,7 +1450,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CF: No peer customers with similar buying patterns found (zero similarity). | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+          <t>Recommendations generated successfully.</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1467,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>None (No unseen peer products)</t>
+          <t>Marker Box, Notebook A, Stapler</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1457,7 +1477,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CF: Similar peers exist, but no unseen products remain to recommend. | Association: All orders in current transaction dataset contain only 1 item. Association rules require multi-item baskets.</t>
+          <t>Recommendations generated successfully.</t>
         </is>
       </c>
     </row>
